--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486868_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486868_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2606</v>
+        <v>5.5176</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9932</v>
+        <v>7.0131</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7326</v>
+        <v>-1.4955</v>
       </c>
       <c r="G2" t="n">
         <v>2.6942</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0573</v>
+        <v>-0.6858</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9218</v>
+        <v>-0.0583</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8646</v>
+        <v>-0.6274</v>
       </c>
       <c r="V2" t="n">
         <v>4.1252</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5653</v>
+        <v>4.4969</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1909</v>
+        <v>4.1522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3743</v>
+        <v>0.3447</v>
       </c>
       <c r="G3" t="n">
         <v>0.9693000000000001</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8752</v>
+        <v>0.8068</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4493</v>
+        <v>0.4106</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4259</v>
+        <v>0.3962</v>
       </c>
       <c r="V3" t="n">
         <v>1.8993</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4943</v>
+        <v>2.5171</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5188</v>
+        <v>2.1404</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0245</v>
+        <v>0.3767</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2616</v>
+        <v>0.7571</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8458</v>
+        <v>0.4993</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1074</v>
+        <v>0.2579</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1157</v>
+        <v>1.6562</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3923</v>
+        <v>1.0512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7234</v>
+        <v>0.605</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3773</v>
+        <v>-0.899</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4535</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.8308</v>
+        <v>-0.3472</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7559</v>
+        <v>0.7332</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2512</v>
+        <v>0.4842</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5047</v>
+        <v>0.249</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.704</v>
+        <v>2.3816</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1791</v>
+        <v>2.6433</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5249</v>
+        <v>-0.2617</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7571</v>
+        <v>-0.2616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4993</v>
+        <v>1.8458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2579</v>
+        <v>-2.1074</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6562</v>
+        <v>2.1157</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0512</v>
+        <v>1.3923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.605</v>
+        <v>0.7234</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.899</v>
+        <v>-2.3773</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.4535</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3472</v>
+        <v>-2.8308</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9202</v>
+        <v>0.6432</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5229</v>
+        <v>0.3756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3973</v>
+        <v>0.2675</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1081</v>
+        <v>1.1363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3456</v>
+        <v>1.3528</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4537</v>
+        <v>-0.2166</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0911</v>
@@ -922,13 +922,13 @@
         <v>3.0801</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3374</v>
+        <v>-0.093</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1702</v>
+        <v>-0.1629</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1672</v>
+        <v>0.0699</v>
       </c>
       <c r="V6" t="n">
         <v>0.2402</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1368</v>
+        <v>-1.1179</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4785</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3416</v>
+        <v>-0.196</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5692</v>
+        <v>-0.8554</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0118</v>
+        <v>-0.6002</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.581</v>
+        <v>-0.2552</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5415</v>
+        <v>-0.6584</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3927</v>
+        <v>-0.6584</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9342</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0278</v>
+        <v>-0.197</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6191</v>
+        <v>0.0582</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6468</v>
+        <v>-0.2552</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.0801</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8818</v>
+        <v>-0.4678</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4729</v>
+        <v>-0.2635</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4089</v>
+        <v>-0.2043</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2875</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2727</v>
+        <v>-1.3534</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9878</v>
+        <v>-3.5172</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2849</v>
+        <v>2.1638</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8554</v>
+        <v>-2.5692</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6002</v>
+        <v>1.0118</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2552</v>
+        <v>-3.581</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6584</v>
+        <v>-1.5415</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6584</v>
+        <v>0.3927</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.9342</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.197</v>
+        <v>-1.0278</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0582</v>
+        <v>0.6191</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2552</v>
+        <v>-1.6468</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>3.0801</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6226</v>
+        <v>-1.0984</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2933</v>
+        <v>-0.5868</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2875</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4819</v>
+        <v>-2.0883</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7503</v>
+        <v>-1.4753</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7316</v>
+        <v>-0.613</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5811</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2848</v>
+        <v>-0.8911</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6433</v>
+        <v>-0.3682</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6415</v>
+        <v>-0.5229</v>
       </c>
       <c r="V9" t="n">
         <v>0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6296</v>
+        <v>-2.3768</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3374</v>
+        <v>-2.2328</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2922</v>
+        <v>-0.144</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3599</v>
@@ -1234,13 +1234,13 @@
         <v>3.0801</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1178</v>
+        <v>-0.865</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5465</v>
+        <v>-0.4419</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5713</v>
+        <v>-0.4231</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6787</v>
+        <v>-3.2241</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4637</v>
+        <v>-3.9795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.785</v>
+        <v>0.7554</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2712</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.112</v>
+        <v>0.5666</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3139</v>
+        <v>0.1704</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4259</v>
+        <v>0.3962</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6982</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9421</v>
+        <v>-3.4561</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5469</v>
+        <v>-3.8535</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6048</v>
+        <v>0.3973</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7457</v>
@@ -1390,13 +1390,13 @@
         <v>2.8748</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1882</v>
+        <v>-0.7022</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1044</v>
+        <v>-0.4109</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0839</v>
+        <v>-0.2913</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8295</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.774299999999999</v>
+        <v>2.432900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6630000000000003</v>
+        <v>1.321599999999999</v>
       </c>
       <c r="F13" t="n">
         <v>1.1111</v>
@@ -1441,7 +1441,7 @@
         <v>-13.3532</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4231</v>
+        <v>4.423100000000001</v>
       </c>
       <c r="K13" t="n">
         <v>3.2812</v>
@@ -1468,28 +1468,28 @@
         <v>21.5609</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.712</v>
+        <v>-2.0535</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4354</v>
+        <v>-0.7765</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2769</v>
+        <v>-1.277</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6138</v>
+        <v>6.613800000000002</v>
       </c>
       <c r="W13" t="n">
         <v>12.049</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.435</v>
+        <v>-5.435000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. OKEKE</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5223</v>
+        <v>3.1941</v>
       </c>
       <c r="E14" t="n">
-        <v>1.131</v>
+        <v>4.8836</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3913</v>
+        <v>-1.6895</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9624</v>
+        <v>6.6711</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6965</v>
+        <v>-0.3668</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2659</v>
+        <v>7.0379</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2698</v>
+        <v>8.6691</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1908</v>
+        <v>0.9607</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0789</v>
+        <v>7.7085</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6927</v>
+        <v>-1.9981</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5057</v>
+        <v>-1.3275</v>
       </c>
       <c r="O14" t="n">
-        <v>0.187</v>
+        <v>-0.6706</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.616</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0534</v>
+        <v>-4.1068</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4777</v>
+        <v>0.9337</v>
       </c>
       <c r="T14" t="n">
-        <v>0.736</v>
+        <v>0.3213</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2583</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6982</v>
+        <v>-2.3573</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4805</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>I. OKEKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7366</v>
+        <v>2.0533</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9422</v>
+        <v>0.2941</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2056</v>
+        <v>1.7592</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6711</v>
+        <v>1.9624</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3668</v>
+        <v>1.6965</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0379</v>
+        <v>0.2659</v>
       </c>
       <c r="J15" t="n">
-        <v>8.6691</v>
+        <v>1.2698</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9607</v>
+        <v>1.1908</v>
       </c>
       <c r="L15" t="n">
-        <v>7.7085</v>
+        <v>0.0789</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9981</v>
+        <v>0.6927</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3275</v>
+        <v>0.5057</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6706</v>
+        <v>0.187</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.616</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-2.0534</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-4.1068</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5238</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6201</v>
+        <v>-0.1008</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0963</v>
+        <v>0.1096</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.3573</v>
+        <v>0.6982</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3573</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.116</v>
+        <v>1.3355</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6654</v>
+        <v>0.95</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4506</v>
+        <v>0.3855</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1722</v>
+        <v>1.5311</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9301</v>
+        <v>-2.2707</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7579</v>
+        <v>3.8017</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6605</v>
+        <v>1.9374</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3977</v>
+        <v>-2.1402</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7372</v>
+        <v>4.0776</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4883</v>
+        <v>-0.4064</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4676</v>
+        <v>-0.1305</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0207</v>
+        <v>-0.2759</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6427</v>
+        <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4427</v>
+        <v>0.8126</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9064</v>
+        <v>-0.1126</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4636</v>
+        <v>0.9253</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9384</v>
+        <v>-1.4189</v>
       </c>
       <c r="W16" t="n">
         <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2755</v>
+        <v>1.327</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.107</v>
+        <v>0.3516</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3825</v>
+        <v>0.9754</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9577</v>
+        <v>1.1722</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4317</v>
+        <v>1.9301</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3893</v>
+        <v>-0.7579</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3808</v>
+        <v>1.6605</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0389</v>
+        <v>2.3977</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3418</v>
+        <v>-0.7372</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4231</v>
+        <v>-0.4883</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4706</v>
+        <v>-0.4676</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0475</v>
+        <v>-0.0207</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4611</v>
+        <v>0.5926</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0979</v>
+        <v>0.0612</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6982</v>
+        <v>0.9384</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1483</v>
+        <v>0.5352</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1132</v>
+        <v>0.1022</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0351</v>
+        <v>0.433</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5311</v>
+        <v>0.9577</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2707</v>
+        <v>-0.4317</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8017</v>
+        <v>1.3893</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9374</v>
+        <v>1.3808</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1402</v>
+        <v>0.0389</v>
       </c>
       <c r="L18" t="n">
-        <v>4.0776</v>
+        <v>1.3418</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4064</v>
+        <v>-0.4231</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1305</v>
+        <v>-0.4706</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2759</v>
+        <v>0.0475</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4641</v>
+        <v>0.2053</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3746</v>
+        <v>-0.2993</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9494</v>
+        <v>-0.2519</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5749</v>
+        <v>-0.0474</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4189</v>
+        <v>0.6982</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5975</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2587</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9112</v>
+        <v>-0.8066</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6525</v>
+        <v>0.7327</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2718</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2739</v>
+        <v>1.4586</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6042</v>
+        <v>0.7088</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6696</v>
+        <v>0.7498</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2875</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6355</v>
+        <v>-0.8371</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0455</v>
+        <v>-2.8795</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.59</v>
+        <v>2.0423</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7375</v>
+        <v>0.2199</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4589</v>
+        <v>-0.7457</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2786</v>
+        <v>0.9656</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4124</v>
+        <v>0.1449</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9913</v>
+        <v>-0.4467</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4211</v>
+        <v>0.5916</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3251</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4676</v>
+        <v>-0.299</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8575</v>
+        <v>0.374</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2321</v>
+        <v>-3.0801</v>
       </c>
       <c r="Q20" t="n">
+        <v>-5.1336</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.0534</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.5743</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.4883</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.5975</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.5975</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.2321</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.0486</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.3669</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.6816</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.1786</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3828</v>
+        <v>-1.6414</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8795</v>
+        <v>-1.3007</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4966</v>
+        <v>-0.3408</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2199</v>
+        <v>-3.7375</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7457</v>
+        <v>-2.4589</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9656</v>
+        <v>-1.2786</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1449</v>
+        <v>-2.4124</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4467</v>
+        <v>-1.9913</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5916</v>
+        <v>-0.4211</v>
       </c>
       <c r="M21" t="n">
-        <v>0.07489999999999999</v>
+        <v>-1.3251</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.299</v>
+        <v>-0.4676</v>
       </c>
       <c r="O21" t="n">
-        <v>0.374</v>
+        <v>-0.8575</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.0801</v>
+        <v>1.2321</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.1336</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1201</v>
+        <v>2.0427</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4883</v>
+        <v>1.1117</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6317</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5975</v>
+        <v>-1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7463</v>
+        <v>-2.0549</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7401</v>
+        <v>-1.8447</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0061</v>
+        <v>-0.2102</v>
       </c>
       <c r="G22" t="n">
         <v>1.5217</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3214</v>
+        <v>0.0127</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3566</v>
+        <v>-0.4612</v>
       </c>
       <c r="U22" t="n">
-        <v>0.678</v>
+        <v>0.4739</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3573</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5494</v>
+        <v>-2.8224</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2796</v>
+        <v>-0.8612</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2698</v>
+        <v>-1.9612</v>
       </c>
       <c r="G23" t="n">
         <v>0.2878</v>
@@ -2248,13 +2248,13 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2746</v>
+        <v>0.4524</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4611</v>
+        <v>-0.0427</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1865</v>
+        <v>0.4951</v>
       </c>
       <c r="V23" t="n">
         <v>-2.9466</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.774</v>
+        <v>1.015400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.111100000000001</v>
+        <v>-1.1112</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6629000000000003</v>
+        <v>2.1264</v>
       </c>
       <c r="G24" t="n">
         <v>9.314600000000002</v>
@@ -2302,7 +2302,7 @@
         <v>13.7376</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7574000000000005</v>
+        <v>-0.7574000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>14.4949</v>
@@ -2326,13 +2326,13 @@
         <v>14.3739</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7122</v>
+        <v>5.5015</v>
       </c>
       <c r="T24" t="n">
         <v>1.2769</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4354</v>
+        <v>4.2248</v>
       </c>
       <c r="V24" t="n">
         <v>-6.6139</v>
